--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_331_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_331_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.807700000000001</v>
+        <v>8.1265</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0427</v>
+        <v>6.2353</v>
       </c>
       <c r="F2" t="n">
-        <v>2.765</v>
+        <v>1.8912</v>
       </c>
       <c r="G2" t="n">
         <v>4.2348</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5729</v>
+        <v>-0.1083</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1949</v>
+        <v>-1.0023</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7678</v>
+        <v>0.894</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0633</v>
+        <v>6.6326</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4052</v>
+        <v>6.0081</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6581</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>6.0085</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5909</v>
+        <v>0.1601</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0474</v>
+        <v>-0.3497</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5434</v>
+        <v>0.5098</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8637</v>
+        <v>2.9892</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2952</v>
+        <v>2.4878</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5686</v>
+        <v>0.5014</v>
       </c>
       <c r="G4" t="n">
         <v>1.7621</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2179</v>
+        <v>-0.0925</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7389</v>
+        <v>-0.5463</v>
       </c>
       <c r="U4" t="n">
-        <v>0.521</v>
+        <v>0.4538</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6097</v>
+        <v>2.2056</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0925</v>
+        <v>2.2852</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4828</v>
+        <v>-0.0795</v>
       </c>
       <c r="G5" t="n">
         <v>4.9332</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4859</v>
+        <v>0.11</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5149</v>
+        <v>-0.3222</v>
       </c>
       <c r="U5" t="n">
-        <v>0.029</v>
+        <v>0.4323</v>
       </c>
       <c r="V5" t="n">
         <v>-1.214</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3435</v>
+        <v>1.3771</v>
       </c>
       <c r="E6" t="n">
         <v>1.3318</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0116</v>
+        <v>0.0452</v>
       </c>
       <c r="G6" t="n">
         <v>1.1638</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1797</v>
+        <v>0.2133</v>
       </c>
       <c r="T6" t="n">
         <v>0.1573</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4644</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.541</v>
+        <v>-2.1741</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0054</v>
+        <v>2.2407</v>
       </c>
       <c r="G7" t="n">
         <v>-2.7269</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3536</v>
+        <v>-0.0442</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3778</v>
+        <v>-0.2552</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0242</v>
+        <v>0.2111</v>
       </c>
       <c r="V7" t="n">
         <v>1.214</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2977</v>
+        <v>-0.3398</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2774</v>
+        <v>0.6937</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0203</v>
+        <v>-1.0336</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9192</v>
+        <v>0.3224</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3526</v>
+        <v>0.299</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2719</v>
+        <v>0.0234</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4637</v>
+        <v>0.8941</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1028</v>
+        <v>0.1849</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6391</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3829</v>
+        <v>-0.5717</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2499</v>
+        <v>0.1141</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6327</v>
+        <v>-0.6859</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2478</v>
+        <v>0.0905</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2592</v>
+        <v>-0.2003</v>
       </c>
       <c r="U8" t="n">
-        <v>0.507</v>
+        <v>0.2908</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5752</v>
+        <v>-0.341</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0349</v>
+        <v>-0.3207</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4597</v>
+        <v>-0.0203</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5862</v>
+        <v>-0.9192</v>
       </c>
       <c r="H9" t="n">
-        <v>2.366</v>
+        <v>1.3526</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.9522</v>
+        <v>-2.2719</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9818</v>
+        <v>0.4637</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9697</v>
+        <v>1.1028</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.9514</v>
+        <v>-0.6391</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6044</v>
+        <v>-1.3829</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3963</v>
+        <v>0.2499</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0008</v>
+        <v>-1.6327</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2183</v>
+        <v>0.2045</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1949</v>
+        <v>-0.3025</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9766</v>
+        <v>0.507</v>
       </c>
       <c r="V9" t="n">
         <v>0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1552</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1473</v>
+        <v>-1.4884</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3024</v>
+        <v>0.9556</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3224</v>
+        <v>-2.5862</v>
       </c>
       <c r="H10" t="n">
-        <v>0.299</v>
+        <v>2.366</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0234</v>
+        <v>-4.9522</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8941</v>
+        <v>-0.9818</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1849</v>
+        <v>1.9697</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7092000000000001</v>
+        <v>-2.9514</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5717</v>
+        <v>-1.6044</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1141</v>
+        <v>0.3963</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6859</v>
+        <v>-2.0008</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7248</v>
+        <v>-0.1759</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7468</v>
+        <v>-0.6484</v>
       </c>
       <c r="U10" t="n">
-        <v>0.022</v>
+        <v>0.4725</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7778</v>
+        <v>-1.1819</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3007</v>
+        <v>-1.1081</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4771</v>
+        <v>-0.0738</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8409</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7925</v>
+        <v>-0.1966</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8215</v>
+        <v>-0.6289</v>
       </c>
       <c r="U11" t="n">
-        <v>0.029</v>
+        <v>0.4323</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8848</v>
+        <v>-1.7936</v>
       </c>
       <c r="E12" t="n">
-        <v>0.121</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0058</v>
+        <v>-1.8713</v>
       </c>
       <c r="G12" t="n">
         <v>0.2106</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1212</v>
+        <v>0.2124</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1019</v>
+        <v>-0.1452</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2232</v>
+        <v>0.3576</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6805</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4616</v>
+        <v>17.2085</v>
       </c>
       <c r="E13" t="n">
-        <v>13.2817</v>
+        <v>14.0283</v>
       </c>
       <c r="F13" t="n">
-        <v>3.180000000000001</v>
+        <v>3.180099999999999</v>
       </c>
       <c r="G13" t="n">
         <v>11.5622</v>
@@ -1438,7 +1438,7 @@
         <v>11.2783</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2838000000000007</v>
+        <v>0.2838000000000003</v>
       </c>
       <c r="J13" t="n">
         <v>19.9262</v>
@@ -1468,10 +1468,10 @@
         <v>17.3965</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3733000000000001</v>
+        <v>0.3733</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.9905</v>
+        <v>-4.2437</v>
       </c>
       <c r="U13" t="n">
         <v>4.6172</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8952</v>
+        <v>0.7054</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4027</v>
+        <v>0.6776</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5075</v>
+        <v>0.0278</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1558</v>
+        <v>-0.4722</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5799</v>
+        <v>-0.2749</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5758</v>
+        <v>-0.1973</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1011</v>
+        <v>1.1214</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2115</v>
+        <v>0.1043</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1104</v>
+        <v>1.0171</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0547</v>
+        <v>-1.5937</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3684</v>
+        <v>-0.3792</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6862</v>
+        <v>-1.2144</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4453</v>
+        <v>0.34</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8259</v>
+        <v>-0.5856</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6194</v>
+        <v>0.9256</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5367</v>
+        <v>0.0654</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4417</v>
+        <v>2.9829</v>
       </c>
       <c r="F15" t="n">
-        <v>0.095</v>
+        <v>-2.9174</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4722</v>
+        <v>-0.2058</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2749</v>
+        <v>-0.9052</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1973</v>
+        <v>0.6994</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1214</v>
+        <v>2.7646</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1043</v>
+        <v>0.8507</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0171</v>
+        <v>1.9139</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5937</v>
+        <v>-2.9704</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3792</v>
+        <v>-1.756</v>
       </c>
       <c r="O15" t="n">
         <v>-1.2144</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1713</v>
+        <v>0.2713</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8215</v>
+        <v>-0.7664</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9928</v>
+        <v>1.0376</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1301</v>
+        <v>0.0023</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1052</v>
+        <v>0.577</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9751</v>
+        <v>-0.5747</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8102</v>
+        <v>-2.1558</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8371</v>
+        <v>-0.5799</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0269</v>
+        <v>-1.5758</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1232</v>
+        <v>-0.1011</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7857</v>
+        <v>-0.2115</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6625</v>
+        <v>0.1104</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.687</v>
+        <v>-2.0547</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0514</v>
+        <v>-0.3684</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.6862</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7084</v>
+        <v>0.5524</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3882</v>
+        <v>0.0002</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3203</v>
+        <v>0.5522</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>F. FERRARI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0081</v>
+        <v>-0.0142</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6866</v>
+        <v>-0.1438</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6948</v>
+        <v>0.1296</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9215</v>
+        <v>0.9208</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5606</v>
+        <v>-0.4645</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6391</v>
+        <v>1.3853</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9502</v>
+        <v>1.2282</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5391</v>
+        <v>0.0504</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5889</v>
+        <v>1.1778</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0287</v>
+        <v>-0.3074</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0216</v>
+        <v>-0.5149</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0502</v>
+        <v>0.2075</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3756</v>
+        <v>0.1346</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2636</v>
+        <v>-0.2122</v>
       </c>
       <c r="U17" t="n">
-        <v>0.112</v>
+        <v>0.3468</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. FERRARI</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2837</v>
+        <v>-0.1777</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3797</v>
+        <v>-1.0405</v>
       </c>
       <c r="F18" t="n">
-        <v>0.096</v>
+        <v>0.8628</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9208</v>
+        <v>-0.9215</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4645</v>
+        <v>-1.5606</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3853</v>
+        <v>0.6391</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2282</v>
+        <v>-0.9502</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0504</v>
+        <v>-1.5391</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1778</v>
+        <v>0.5889</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3074</v>
+        <v>0.0287</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5149</v>
+        <v>-0.0216</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2075</v>
+        <v>0.0502</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1349</v>
+        <v>0.1898</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4481</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3132</v>
+        <v>0.2801</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1418</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4457</v>
+        <v>-0.8808</v>
       </c>
       <c r="E19" t="n">
-        <v>2.629</v>
+        <v>-0.6331</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0747</v>
+        <v>-0.2477</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2058</v>
+        <v>0.3183</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9052</v>
+        <v>-0.0431</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6994</v>
+        <v>0.3614</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7646</v>
+        <v>2.2915</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8507</v>
+        <v>1.3983</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9139</v>
+        <v>0.8932</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9704</v>
+        <v>-1.9733</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.756</v>
+        <v>-1.4414</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2144</v>
+        <v>-0.5319</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2399</v>
+        <v>-0.0393</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1202</v>
+        <v>-0.6051</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8804</v>
+        <v>0.5658</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4121</v>
+        <v>-1.1072</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1469</v>
+        <v>1.1741</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2652</v>
+        <v>-2.2813</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5751</v>
+        <v>1.3587</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.839</v>
+        <v>0.0805</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7361</v>
+        <v>1.2781</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4669</v>
+        <v>1.8237</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4166</v>
+        <v>0.8066</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0502</v>
+        <v>1.0171</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1082</v>
+        <v>-0.4651</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4223</v>
+        <v>-0.7261</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6859</v>
+        <v>0.261</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.4659</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3791</v>
+        <v>-0.1357</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4177</v>
+        <v>-1.1173</v>
       </c>
       <c r="E21" t="n">
-        <v>0.259</v>
+        <v>0.6898</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6767</v>
+        <v>-1.807</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0862</v>
+        <v>-1.8102</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1259</v>
+        <v>-1.8371</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9603</v>
+        <v>0.0269</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5801</v>
+        <v>-0.1232</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9579</v>
+        <v>-0.7857</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6222</v>
+        <v>0.6625</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6663</v>
+        <v>-1.687</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0838</v>
+        <v>-1.0514</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5825</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.7112</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.639</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3049</v>
+        <v>0.461</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9709</v>
+        <v>-0.0272</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2757</v>
+        <v>0.4883</v>
       </c>
       <c r="V21" t="n">
-        <v>3.0748</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>4.2888</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5841</v>
+        <v>-1.187</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0561</v>
+        <v>-0.911</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6402</v>
+        <v>-0.2759</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3587</v>
+        <v>-1.5751</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0805</v>
+        <v>-0.839</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2781</v>
+        <v>-0.7361</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8237</v>
+        <v>-0.4669</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8066</v>
+        <v>-0.4166</v>
       </c>
       <c r="L22" t="n">
-        <v>1.0171</v>
+        <v>-0.0502</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4651</v>
+        <v>-1.1082</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7261</v>
+        <v>-0.4223</v>
       </c>
       <c r="O22" t="n">
-        <v>0.261</v>
+        <v>-0.6859</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R22" t="n">
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9427</v>
+        <v>0.1562</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4946</v>
+        <v>0.3684</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6278</v>
+        <v>-1.4278</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2229</v>
+        <v>0.4949</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.405</v>
+        <v>-1.9227</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3183</v>
+        <v>-1.0862</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0431</v>
+        <v>-0.1259</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3614</v>
+        <v>-0.9603</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2915</v>
+        <v>1.5801</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3983</v>
+        <v>0.9579</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8932</v>
+        <v>0.6222</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9733</v>
+        <v>-2.6663</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4414</v>
+        <v>-1.0838</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5319</v>
+        <v>-1.5825</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7863</v>
+        <v>0.2948</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1949</v>
+        <v>-0.735</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4086</v>
+        <v>1.0297</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3.0748</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>4.2888</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2272</v>
+        <v>-4.9742</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5259</v>
+        <v>-2.1721</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7013</v>
+        <v>-2.8021</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5877</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6963</v>
+        <v>-0.4433</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1949</v>
+        <v>-0.841</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4986</v>
+        <v>0.3978</v>
       </c>
       <c r="V24" t="n">
         <v>1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.0336</v>
+        <v>-5.5624</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1117</v>
+        <v>-4.8758</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9218</v>
+        <v>-0.6866</v>
       </c>
       <c r="G25" t="n">
         <v>-3.3453</v>
@@ -2404,13 +2404,13 @@
         <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7631</v>
+        <v>-0.2919</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.315</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>0.3943</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.4618</v>
+        <v>-15.6755</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.180000000000001</v>
+        <v>-3.18</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.2817</v>
+        <v>-12.4952</v>
       </c>
       <c r="G26" t="n">
         <v>-11.562</v>
@@ -2452,10 +2452,10 @@
         <v>-11.2782</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2838000000000004</v>
+        <v>-0.2838000000000003</v>
       </c>
       <c r="J26" t="n">
-        <v>8.363899999999999</v>
+        <v>8.363900000000001</v>
       </c>
       <c r="K26" t="n">
         <v>-1.3889</v>
@@ -2473,7 +2473,7 @@
         <v>-10.0367</v>
       </c>
       <c r="P26" t="n">
-        <v>-9.277900000000001</v>
+        <v>-9.277899999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.3965</v>
@@ -2482,13 +2482,13 @@
         <v>8.118599999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3733000000000001</v>
+        <v>1.1597</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.617100000000001</v>
+        <v>-4.6171</v>
       </c>
       <c r="U26" t="n">
-        <v>4.990499999999999</v>
+        <v>5.776900000000001</v>
       </c>
       <c r="V26" t="n">
         <v>4.0052</v>
@@ -2497,7 +2497,7 @@
         <v>10.4695</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.4643</v>
+        <v>-6.464300000000001</v>
       </c>
     </row>
   </sheetData>
